--- a/brain/library/internal/scorecard/Senior Living and Home Care Operating Software Scorecard April 2026.xlsx
+++ b/brain/library/internal/scorecard/Senior Living and Home Care Operating Software Scorecard April 2026.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INITIAL SCREEN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TEMPLATE" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industry Scorecard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_bdm.8018492968a5442495f20d90ab0edcf5.edm" hidden="1">#REF!</definedName>
@@ -837,7 +837,7 @@
     <row r="3">
       <c r="B3" s="61" t="inlineStr">
         <is>
-          <t>XX Initial Screen</t>
+          <t>Senior Living &amp; Home Care Operating Software - Initial Screen</t>
         </is>
       </c>
     </row>
@@ -869,13 +869,21 @@
           <t>Margins</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>15%+ EBITDA margins required</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>70-80% gross margins at scale; EBITDA 20-30% for scaled vendors (PointClickCare, MatrixCare). &gt;15% threshold met.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -883,13 +891,21 @@
           <t>Recurring Revenue</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Existing recurring/contractual revenue or clear path to convert</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Subscription/SaaS model dominant; per-bed/per-user pricing. 80%+ recurring at scaled vendors.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -897,13 +913,21 @@
           <t>Industry Growth</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Growth rate above GDP (~3%+)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>LTC software ~6.9% CAGR; home health software ~13% CAGR. Blended well above GDP.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -911,13 +935,21 @@
           <t>Growth TAM</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>$500M+ total addressable market (investor floor)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>US LTC software $2.4B growing to $4.1B + $4.5B home health = ~$6.9B combined. Far above $500M floor.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="62" t="inlineStr">
@@ -925,7 +957,11 @@
           <t>VERDICT</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PASS — All 4 gates met. Proceed to Industry Scorecard.</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>All 4 must pass to proceed to Industry Scorecard</t>
@@ -945,7 +981,11 @@
           <t>Number of independently owned acquisition candidates</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>30-50 independent vendors in fragmented long tail (point solutions, regional players)</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>Determines sprint duration, not go/no-go</t>
@@ -958,7 +998,11 @@
           <t>Sprint duration estimate</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Focused sprint (20-50 range)</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>50+ = long sprint | 20-50 = focused | 10-20 = fast | &lt;10 = very fast</t>
@@ -1007,7 +1051,7 @@
     <row r="3" customFormat="1" s="28">
       <c r="B3" s="33" t="inlineStr">
         <is>
-          <t>XX Industry Scorecard</t>
+          <t>Senior Living &amp; Home Care Operating Software - Industry Scorecard</t>
         </is>
       </c>
       <c r="C3" s="30" t="n"/>
@@ -1028,7 +1072,7 @@
     <row r="5" ht="14.5" customHeight="1">
       <c r="B5" s="35" t="inlineStr">
         <is>
-          <t>XX  Industry Scorecard</t>
+          <t>Senior Living &amp; Home Care Operating Software  Industry Scorecard</t>
         </is>
       </c>
       <c r="C5" s="36" t="inlineStr">
@@ -1131,9 +1175,8 @@
         </is>
       </c>
       <c r="C9" s="50" t="n"/>
-      <c r="D9" s="56">
-        <f t="array" ref="D9">_xlfn.SWITCH(E9,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D9" s="56" t="n">
+        <v>3</v>
       </c>
       <c r="E9" s="48" t="inlineStr">
         <is>
@@ -1158,7 +1201,7 @@
       </c>
       <c r="J9" s="23" t="inlineStr">
         <is>
-          <t>&gt;10% industry growth</t>
+          <t>LTC software 6.9% CAGR; home health software 13% CAGR — blended ~9-10%, &gt;3x GDP</t>
         </is>
       </c>
     </row>
@@ -1169,13 +1212,12 @@
         </is>
       </c>
       <c r="C10" s="50" t="n"/>
-      <c r="D10" s="56">
-        <f t="array" ref="D10">_xlfn.SWITCH(E10,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D10" s="56" t="n">
+        <v>2</v>
       </c>
       <c r="E10" s="48" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>+/-</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
@@ -1200,7 +1242,7 @@
       </c>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t>Data 'manipulation' is a huge pain point</t>
+          <t>Digital penetration rising but long tail still paper/legacy; strong catalyst from staffing crisis + value-based care</t>
         </is>
       </c>
     </row>
@@ -1211,9 +1253,8 @@
         </is>
       </c>
       <c r="C11" s="50" t="n"/>
-      <c r="D11" s="56">
-        <f t="array" ref="D11">_xlfn.SWITCH(E11,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D11" s="56" t="n">
+        <v>3</v>
       </c>
       <c r="E11" s="48" t="inlineStr">
         <is>
@@ -1236,7 +1277,11 @@
           <t>Mostly Headwinds</t>
         </is>
       </c>
-      <c r="J11" s="23" t="n"/>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t>Aging demographics (80+ pop doubling by 2040), staffing shortages drive automation demand, VBC reimbursement shifts</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
       <c r="B12" s="19" t="inlineStr">
@@ -1245,13 +1290,12 @@
         </is>
       </c>
       <c r="C12" s="51" t="n"/>
-      <c r="D12" s="57">
-        <f t="array" ref="D12">_xlfn.SWITCH(E12,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D12" s="57" t="n">
+        <v>3</v>
       </c>
       <c r="E12" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="F12" s="21" t="n"/>
@@ -1272,7 +1316,7 @@
       </c>
       <c r="J12" s="24" t="inlineStr">
         <is>
-          <t>Data 'manipulation' is a huge pain point</t>
+          <t>CMS PDPM/PDGM, Medicare Advantage growth, EHR interoperability mandates, nursing shortage all pushing tech adoption</t>
         </is>
       </c>
     </row>
@@ -1301,13 +1345,12 @@
         </is>
       </c>
       <c r="C14" s="50" t="n"/>
-      <c r="D14" s="56">
-        <f t="array" ref="D14">_xlfn.SWITCH(E14,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D14" s="56" t="n">
+        <v>2</v>
       </c>
       <c r="E14" s="48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+/-</t>
         </is>
       </c>
       <c r="F14" s="9" t="n"/>
@@ -1328,7 +1371,7 @@
       </c>
       <c r="J14" s="23" t="inlineStr">
         <is>
-          <t>~7 well-known players</t>
+          <t>Dozens of major vendors + long tail of point solutions — hundreds when including niche tools</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1382,12 @@
         </is>
       </c>
       <c r="C15" s="51" t="n"/>
-      <c r="D15" s="57">
-        <f t="array" ref="D15">_xlfn.SWITCH(E15,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D15" s="57" t="n">
+        <v>1</v>
       </c>
       <c r="E15" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F15" s="21" t="n"/>
@@ -1366,7 +1408,7 @@
       </c>
       <c r="J15" s="24" t="inlineStr">
         <is>
-          <t>Largest has ~35% of market</t>
+          <t>PointClickCare ~22-26%; MatrixCare + WellSky + PCC concentrate top tier &gt;50% at scaled operator level</t>
         </is>
       </c>
     </row>
@@ -1395,9 +1437,8 @@
         </is>
       </c>
       <c r="C17" s="50" t="n"/>
-      <c r="D17" s="56">
-        <f t="array" ref="D17">_xlfn.SWITCH(E17,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D17" s="56" t="n">
+        <v>3</v>
       </c>
       <c r="E17" s="48" t="inlineStr">
         <is>
@@ -1422,7 +1463,7 @@
       </c>
       <c r="J17" s="23" t="inlineStr">
         <is>
-          <t>~80%/~55% recurring/non-rec gross margin</t>
+          <t>70-80% gross margins at scale for SaaS vendors</t>
         </is>
       </c>
     </row>
@@ -1433,13 +1474,12 @@
         </is>
       </c>
       <c r="C18" s="50" t="n"/>
-      <c r="D18" s="56">
-        <f t="array" ref="D18">_xlfn.SWITCH(E18,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D18" s="56" t="n">
+        <v>2</v>
       </c>
       <c r="E18" s="48" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>+/-</t>
         </is>
       </c>
       <c r="F18" s="9" t="n"/>
@@ -1460,7 +1500,7 @@
       </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t>Probably close to 30%</t>
+          <t>20-30% EBITDA at scaled vendors; sub-scale players 10-20%</t>
         </is>
       </c>
     </row>
@@ -1471,13 +1511,12 @@
         </is>
       </c>
       <c r="C19" s="51" t="n"/>
-      <c r="D19" s="57">
-        <f t="array" ref="D19">_xlfn.SWITCH(E19,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D19" s="57" t="n">
+        <v>2</v>
       </c>
       <c r="E19" s="48" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>+/-</t>
         </is>
       </c>
       <c r="F19" s="21" t="n"/>
@@ -1498,7 +1537,7 @@
       </c>
       <c r="J19" s="24" t="inlineStr">
         <is>
-          <t>Probably close to 20%</t>
+          <t>10-20% ROTC for mature SaaS; higher for scaled incumbents</t>
         </is>
       </c>
     </row>
@@ -1527,13 +1566,12 @@
         </is>
       </c>
       <c r="C21" s="50" t="n"/>
-      <c r="D21" s="56">
-        <f t="array" ref="D21">_xlfn.SWITCH(E21,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D21" s="56" t="n">
+        <v>2</v>
       </c>
       <c r="E21" s="48" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>+/-</t>
         </is>
       </c>
       <c r="F21" s="9" t="n"/>
@@ -1554,7 +1592,7 @@
       </c>
       <c r="J21" s="23" t="inlineStr">
         <is>
-          <t>Outstanding customer feedback</t>
+          <t>Mixed — operators depend on software for billing/compliance but complain about usability and incumbent pricing</t>
         </is>
       </c>
     </row>
@@ -1565,13 +1603,12 @@
         </is>
       </c>
       <c r="C22" s="50" t="n"/>
-      <c r="D22" s="56">
-        <f t="array" ref="D22">_xlfn.SWITCH(E22,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D22" s="56" t="n">
+        <v>3</v>
       </c>
       <c r="E22" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="F22" s="9" t="n"/>
@@ -1592,7 +1629,7 @@
       </c>
       <c r="J22" s="23" t="inlineStr">
         <is>
-          <t>Weaker value proposition</t>
+          <t>Clear ROI: MDS/OASIS compliance, billing, census, EHR — regulatory-mandated workflows</t>
         </is>
       </c>
     </row>
@@ -1603,13 +1640,12 @@
         </is>
       </c>
       <c r="C23" s="51" t="n"/>
-      <c r="D23" s="57">
-        <f t="array" ref="D23">_xlfn.SWITCH(E23,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D23" s="57" t="n">
+        <v>3</v>
       </c>
       <c r="E23" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="F23" s="21" t="n"/>
@@ -1630,7 +1666,7 @@
       </c>
       <c r="J23" s="24" t="inlineStr">
         <is>
-          <t>Can be replaced w/effort</t>
+          <t>High switching costs — clinical data migration, staff retraining, 7-10 yr replacement cycles</t>
         </is>
       </c>
     </row>
@@ -1659,9 +1695,8 @@
         </is>
       </c>
       <c r="C25" s="50" t="n"/>
-      <c r="D25" s="56">
-        <f t="array" ref="D25">_xlfn.SWITCH(E25,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D25" s="56" t="n">
+        <v>3</v>
       </c>
       <c r="E25" s="48" t="inlineStr">
         <is>
@@ -1686,7 +1721,7 @@
       </c>
       <c r="J25" s="23" t="inlineStr">
         <is>
-          <t>High visibility</t>
+          <t>Tech direction clear — cloud SaaS, mobile point-of-care, AI documentation; low obsolescence risk</t>
         </is>
       </c>
     </row>
@@ -1697,13 +1732,12 @@
         </is>
       </c>
       <c r="C26" s="50" t="n"/>
-      <c r="D26" s="56">
-        <f t="array" ref="D26">_xlfn.SWITCH(E26,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D26" s="56" t="n">
+        <v>1</v>
       </c>
       <c r="E26" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F26" s="9" t="n"/>
@@ -1724,7 +1758,7 @@
       </c>
       <c r="J26" s="23" t="inlineStr">
         <is>
-          <t>Some risk and frequency</t>
+          <t>Heavy regulatory — HIPAA, CMS rules, state survey requirements; frequent reimbursement policy changes</t>
         </is>
       </c>
     </row>
@@ -1735,9 +1769,8 @@
         </is>
       </c>
       <c r="C27" s="50" t="n"/>
-      <c r="D27" s="56">
-        <f t="array" ref="D27">_xlfn.SWITCH(E27,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D27" s="56" t="n">
+        <v>2</v>
       </c>
       <c r="E27" s="48" t="inlineStr">
         <is>
@@ -1762,7 +1795,7 @@
       </c>
       <c r="J27" s="23" t="inlineStr">
         <is>
-          <t>Some liability risks</t>
+          <t>HIPAA/PHI liability real but manageable; operator bears primary regulatory risk</t>
         </is>
       </c>
     </row>
@@ -1773,9 +1806,8 @@
         </is>
       </c>
       <c r="C28" s="50" t="n"/>
-      <c r="D28" s="56">
-        <f t="array" ref="D28">_xlfn.SWITCH(E28,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D28" s="56" t="n">
+        <v>3</v>
       </c>
       <c r="E28" s="48" t="inlineStr">
         <is>
@@ -1800,7 +1832,7 @@
       </c>
       <c r="J28" s="23" t="inlineStr">
         <is>
-          <t>Low cyclicality</t>
+          <t>Low cyclicality — demand for LTC/home care inelastic, aging demographics secular</t>
         </is>
       </c>
     </row>
@@ -1811,13 +1843,12 @@
         </is>
       </c>
       <c r="C29" s="51" t="n"/>
-      <c r="D29" s="57">
-        <f t="array" ref="D29">_xlfn.SWITCH(E29,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D29" s="57" t="n">
+        <v>1</v>
       </c>
       <c r="E29" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F29" s="21" t="n"/>
@@ -1838,7 +1869,7 @@
       </c>
       <c r="J29" s="24" t="inlineStr">
         <is>
-          <t>Some resiliency to trends</t>
+          <t>Reimbursement squeeze on operators (Medicaid rates, MA) pressures software budgets downstream</t>
         </is>
       </c>
     </row>
@@ -1867,13 +1898,12 @@
         </is>
       </c>
       <c r="C31" s="50" t="n"/>
-      <c r="D31" s="56">
-        <f t="array" ref="D31">_xlfn.SWITCH(E31,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D31" s="56" t="n">
+        <v>2</v>
       </c>
       <c r="E31" s="48" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>+/-</t>
         </is>
       </c>
       <c r="F31" s="9" t="n"/>
@@ -1894,7 +1924,7 @@
       </c>
       <c r="J31" s="23" t="inlineStr">
         <is>
-          <t>No VC-backed companies (only PE-owned)</t>
+          <t>Moderate VC activity in AI-documentation &amp; home care scheduling (August, CareAcademy); not overrun</t>
         </is>
       </c>
     </row>
@@ -1905,9 +1935,8 @@
         </is>
       </c>
       <c r="C32" s="50" t="n"/>
-      <c r="D32" s="56">
-        <f t="array" ref="D32">_xlfn.SWITCH(E32,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D32" s="56" t="n">
+        <v>1</v>
       </c>
       <c r="E32" s="48" t="inlineStr">
         <is>
@@ -1932,7 +1961,7 @@
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>High competition</t>
+          <t>High — PCC, MatrixCare, WellSky dominate; incumbents bar-raising with AI features</t>
         </is>
       </c>
     </row>
@@ -1943,13 +1972,12 @@
         </is>
       </c>
       <c r="C33" s="50" t="n"/>
-      <c r="D33" s="56">
-        <f t="array" ref="D33">_xlfn.SWITCH(E33,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D33" s="56" t="n">
+        <v>2</v>
       </c>
       <c r="E33" s="48" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>+/-</t>
         </is>
       </c>
       <c r="F33" s="9" t="n"/>
@@ -1970,7 +1998,7 @@
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>No new entrants</t>
+          <t>Some new entrants in AI point solutions; incumbents acquiring/bundling aggressively</t>
         </is>
       </c>
     </row>
@@ -2016,9 +2044,8 @@
         </is>
       </c>
       <c r="C35" s="50" t="n"/>
-      <c r="D35" s="56">
-        <f t="array" ref="D35">_xlfn.SWITCH(E35,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D35" s="56" t="n">
+        <v>2</v>
       </c>
       <c r="E35" s="48" t="inlineStr">
         <is>
@@ -2043,7 +2070,7 @@
       </c>
       <c r="J35" s="23" t="inlineStr">
         <is>
-          <t>Some customer power</t>
+          <t>Operators consolidating (national chains) increases customer power at top; SMB long tail low power</t>
         </is>
       </c>
     </row>
@@ -2054,13 +2081,12 @@
         </is>
       </c>
       <c r="C36" s="51" t="n"/>
-      <c r="D36" s="57">
-        <f t="array" ref="D36">_xlfn.SWITCH(E36,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D36" s="57" t="n">
+        <v>1</v>
       </c>
       <c r="E36" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F36" s="21" t="n"/>
@@ -2081,7 +2107,7 @@
       </c>
       <c r="J36" s="24" t="inlineStr">
         <is>
-          <t>Some substitutes</t>
+          <t>Incumbent platforms expanding modules — threat of bundled substitution for point solutions</t>
         </is>
       </c>
     </row>
@@ -2110,9 +2136,8 @@
         </is>
       </c>
       <c r="C38" s="50" t="n"/>
-      <c r="D38" s="56">
-        <f t="array" ref="D38">_xlfn.SWITCH(E38,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D38" s="56" t="n">
+        <v>2</v>
       </c>
       <c r="E38" s="48" t="inlineStr">
         <is>
@@ -2137,7 +2162,7 @@
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>Moderate complexity</t>
+          <t>Moderate complexity — clinical + billing + compliance workflows</t>
         </is>
       </c>
     </row>
@@ -2148,9 +2173,8 @@
         </is>
       </c>
       <c r="C39" s="51" t="n"/>
-      <c r="D39" s="57">
-        <f t="array" ref="D39">_xlfn.SWITCH(E39,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D39" s="57" t="n">
+        <v>2</v>
       </c>
       <c r="E39" s="48" t="inlineStr">
         <is>
@@ -2175,7 +2199,7 @@
       </c>
       <c r="J39" s="24" t="inlineStr">
         <is>
-          <t>Some actionable levers</t>
+          <t>Clear levers — modernize UI, add AI scribe, bundle point solutions, convert perpetual to SaaS</t>
         </is>
       </c>
     </row>
@@ -2204,13 +2228,12 @@
         </is>
       </c>
       <c r="C41" s="50" t="n"/>
-      <c r="D41" s="56">
-        <f t="array" ref="D41">_xlfn.SWITCH(E41,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D41" s="56" t="n">
+        <v>3</v>
       </c>
       <c r="E41" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -2231,7 +2254,7 @@
       </c>
       <c r="J41" s="23" t="inlineStr">
         <is>
-          <t>Neutral impact</t>
+          <t>Net positive — better care coordination for vulnerable seniors, staff retention, compliance</t>
         </is>
       </c>
     </row>
@@ -2242,9 +2265,8 @@
         </is>
       </c>
       <c r="C42" s="52" t="n"/>
-      <c r="D42" s="56">
-        <f t="array" ref="D42">_xlfn.SWITCH(E42,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D42" s="56" t="n">
+        <v>2</v>
       </c>
       <c r="E42" s="48" t="inlineStr">
         <is>
@@ -2269,7 +2291,7 @@
       </c>
       <c r="J42" s="25" t="inlineStr">
         <is>
-          <t>Neutral externalities</t>
+          <t>Positive on care quality; neutral on labor displacement</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2307,7 @@
       </c>
       <c r="D43" s="18" t="inlineStr">
         <is>
-          <t>Commentary: N/A</t>
+          <t>Commentary: Strong market tailwinds and mission-critical workflows offset by incumbent dominance (PCC/MatrixCare/WellSky) and reimbursement squeeze flowing down to operators. Long-tail point solutions present the best acquisition surface.</t>
         </is>
       </c>
       <c r="E43" s="18" t="n"/>
